--- a/UI/src/test/resources/testdata.xlsx
+++ b/UI/src/test/resources/testdata.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shraddha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unmesh\unmesh_intelliJ_workspace\TestAutomationFramework\UI\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84847649-79D2-49D3-BFDC-1199F7E84C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8658288-9765-474D-B8A6-9C2BEB914F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{760E0CB6-5AB1-4957-BDF5-05142EB9CA11}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="UI_Login_Data_Naukri" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
